--- a/软件/一键财报分析/财报模板.xlsx
+++ b/软件/一键财报分析/财报模板.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
     <t>项目</t>
   </si>
@@ -48,6 +48,9 @@
     <t>流动负债合计</t>
   </si>
   <si>
+    <t>非流动负债合计</t>
+  </si>
+  <si>
     <t>负债合计</t>
   </si>
   <si>
@@ -60,31 +63,25 @@
     <t>上期金额</t>
   </si>
   <si>
-    <t>营业总收入</t>
-  </si>
-  <si>
     <t>营业收入</t>
   </si>
   <si>
     <t>营业成本</t>
   </si>
   <si>
-    <t>毛利</t>
-  </si>
-  <si>
     <t>营业利润</t>
   </si>
   <si>
     <t>净利润</t>
   </si>
   <si>
-    <t>经营活动产生的现金流量净额</t>
-  </si>
-  <si>
-    <t>投资活动产生的现金流量净额</t>
-  </si>
-  <si>
-    <t>筹资活动产生的现金流量净额</t>
+    <t>经营活动现金流净额</t>
+  </si>
+  <si>
+    <t>投资活动现金流净额</t>
+  </si>
+  <si>
+    <t>筹资活动现金流净额</t>
   </si>
 </sst>
 </file>
@@ -442,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -461,10 +458,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>50000000</v>
+        <v>5000</v>
       </c>
       <c r="C2">
-        <v>45000000</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -472,10 +469,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>30000000</v>
+        <v>3000</v>
       </c>
       <c r="C3">
-        <v>28000000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -483,10 +480,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>20000000</v>
+        <v>2000</v>
       </c>
       <c r="C4">
-        <v>18000000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -494,10 +491,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>150000000</v>
+        <v>15000</v>
       </c>
       <c r="C5">
-        <v>140000000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -505,10 +502,10 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>80000000</v>
+        <v>10000</v>
       </c>
       <c r="C6">
-        <v>75000000</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -516,10 +513,10 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>250000000</v>
+        <v>25000</v>
       </c>
       <c r="C7">
-        <v>230000000</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -527,10 +524,10 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>80000000</v>
+        <v>6000</v>
       </c>
       <c r="C8">
-        <v>75000000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -538,10 +535,10 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>120000000</v>
+        <v>6000</v>
       </c>
       <c r="C9">
-        <v>110000000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -549,10 +546,21 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>130000000</v>
+        <v>12000</v>
       </c>
       <c r="C10">
-        <v>120000000</v>
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11">
+        <v>13000</v>
+      </c>
+      <c r="C11">
+        <v>12000</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -570,76 +578,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2">
-        <v>200000000</v>
+        <v>20000</v>
       </c>
       <c r="C2">
-        <v>180000000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3">
-        <v>200000000</v>
+        <v>12000</v>
       </c>
       <c r="C3">
-        <v>180000000</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4">
-        <v>120000000</v>
+        <v>3500</v>
       </c>
       <c r="C4">
-        <v>110000000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5">
-        <v>80000000</v>
+        <v>2800</v>
       </c>
       <c r="C5">
-        <v>70000000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>35000000</v>
-      </c>
-      <c r="C6">
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>28000000</v>
-      </c>
-      <c r="C7">
-        <v>24000000</v>
+        <v>2400</v>
       </c>
     </row>
   </sheetData>
@@ -657,43 +643,43 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>32000000</v>
+        <v>3200</v>
       </c>
       <c r="C2">
-        <v>28000000</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>-15000000</v>
+        <v>-1500</v>
       </c>
       <c r="C3">
-        <v>-12000000</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>-5000000</v>
+        <v>-500</v>
       </c>
       <c r="C4">
-        <v>-8000000</v>
+        <v>-800</v>
       </c>
     </row>
   </sheetData>
